--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>14.336</v>
+        <v>18.0018</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6524</v>
+        <v>16.2486</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6835</v>
+        <v>1.7532</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3987</v>
+        <v>4.3509</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2642</v>
+        <v>0.0723999999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1344</v>
+        <v>4.2784</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5543</v>
+        <v>12.7341</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7095</v>
+        <v>3.8339</v>
       </c>
       <c r="L2" t="n">
-        <v>5.8448</v>
+        <v>8.9003</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.155799999999999</v>
+        <v>-8.3832</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4453</v>
+        <v>-3.7614</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.7104</v>
+        <v>-4.6218</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2009</v>
+        <v>0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.8011</v>
+        <v>-8.957800000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>7.002</v>
+        <v>9.9316</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2773</v>
+        <v>6.176399999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6211</v>
+        <v>1.7408</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6562</v>
+        <v>4.4356</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4591</v>
+        <v>6.500999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2782</v>
+        <v>10.7316</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.819</v>
+        <v>-4.230700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0197</v>
+        <v>15.6554</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1804</v>
+        <v>14.027</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1606999999999998</v>
+        <v>1.6285</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1144</v>
+        <v>5.556300000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8348</v>
+        <v>4.8047</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7204</v>
+        <v>0.7517000000000007</v>
       </c>
       <c r="J3" t="n">
-        <v>8.4765</v>
+        <v>17.5908</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1511</v>
+        <v>8.783099999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3252</v>
+        <v>8.807599999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.362</v>
+        <v>-12.0345</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3164</v>
+        <v>-3.9785</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.0456</v>
+        <v>-8.056000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0009</v>
+        <v>6.621</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.0017</v>
+        <v>-7.5948</v>
       </c>
       <c r="R3" t="n">
-        <v>9.0025</v>
+        <v>14.2158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2943</v>
+        <v>-3.5301</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007200000000000095</v>
+        <v>-3.3685</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3015</v>
+        <v>-0.1614999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1987</v>
+        <v>7.0082</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6985</v>
+        <v>7.3995</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4997</v>
+        <v>-0.3913000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7906</v>
+        <v>5.1253</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1524000000000001</v>
+        <v>-0.5830999999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>4.943</v>
+        <v>5.7084</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6983000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="H4" t="n">
-        <v>1.177</v>
+        <v>3.1093</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4787</v>
+        <v>-1.1843</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5646</v>
+        <v>6.336499999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4847</v>
+        <v>4.9907</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0799</v>
+        <v>1.3458</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8662</v>
+        <v>-4.4114</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3077</v>
+        <v>-1.8815</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5586</v>
+        <v>-2.53</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6002000000000001</v>
+        <v>1.7527</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.4013</v>
+        <v>-6.4262</v>
       </c>
       <c r="R4" t="n">
-        <v>5.0014</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6325</v>
+        <v>2.0067</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1647000000000001</v>
+        <v>-1.0519</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4678</v>
+        <v>3.0586</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8596999999999999</v>
+        <v>-0.5589999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3401</v>
+        <v>-1.1179</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4.785</v>
+        <v>2.9405</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1412</v>
+        <v>4.952500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6439</v>
+        <v>-2.012</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4304999999999999</v>
+        <v>2.2879</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1158</v>
+        <v>1.0483</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5463</v>
+        <v>1.2398</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9877</v>
+        <v>5.3927</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0028</v>
+        <v>3.364</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0151</v>
+        <v>2.0289</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4182</v>
+        <v>-3.1048</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.887</v>
+        <v>-2.3156</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5312</v>
+        <v>-0.7891999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>6.4018</v>
+        <v>7.5947</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>6.4018</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3266</v>
+        <v>-1.9477</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0463</v>
+        <v>-1.4663</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2803</v>
+        <v>-0.4812</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8597</v>
+        <v>-4.994400000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0595</v>
+        <v>-6.2155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6648</v>
+        <v>-3.7016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7626000000000004</v>
+        <v>-1.5148</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9021</v>
+        <v>-2.1868</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1215999999999999</v>
+        <v>-0.8687</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8271</v>
+        <v>-0.6029</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.9486</v>
+        <v>-0.2658</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2847</v>
+        <v>-1.2674</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6653</v>
+        <v>-0.6029</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.3806</v>
+        <v>-0.6645</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.4063</v>
+        <v>0.3986999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8382</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.568</v>
+        <v>0.3986999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>2.400700000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8017</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>8.202400000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1741</v>
+        <v>-0.306</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9797</v>
+        <v>-0.2473</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8057000000000001</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5597</v>
+        <v>-2.7216</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2593</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6996</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="7">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5511999999999997</v>
+        <v>-3.9228</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.7467</v>
+        <v>-7.0791</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1956</v>
+        <v>3.1561</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9498</v>
+        <v>0.4888000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009500000000000064</v>
+        <v>3.676</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9404</v>
+        <v>-3.1872</v>
       </c>
       <c r="J7" t="n">
-        <v>1.033</v>
+        <v>3.0459</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8524999999999998</v>
+        <v>3.4177</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8854</v>
+        <v>-0.3718</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9168000000000001</v>
+        <v>-2.5572</v>
       </c>
       <c r="N7" t="n">
-        <v>0.862</v>
+        <v>0.2583</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0549</v>
+        <v>-2.8155</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0003</v>
+        <v>-2.3369</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.0016</v>
+        <v>-10.9053</v>
       </c>
       <c r="R7" t="n">
-        <v>5.0014</v>
+        <v>8.5684</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0595</v>
+        <v>-1.5305</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0628</v>
+        <v>-0.2860999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0034</v>
+        <v>-1.2443</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5602</v>
+        <v>-0.5445000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.8408</v>
+        <v>1.0663</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7194</v>
+        <v>-1.6108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.890999999999999</v>
+        <v>-7.251</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4503</v>
+        <v>-7.132499999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.4407</v>
+        <v>-0.1185</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.5776</v>
+        <v>-5.9747</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3536999999999999</v>
+        <v>2.4815</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.223800000000001</v>
+        <v>-8.456299999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2469</v>
+        <v>5.4217</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3470999999999997</v>
+        <v>6.918</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.594</v>
+        <v>-1.4963</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3306</v>
+        <v>-11.3962</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7009000000000001</v>
+        <v>-4.4364</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.6297</v>
+        <v>-6.96</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2000999999999998</v>
+        <v>2.3368</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.4013</v>
+        <v>-11.2947</v>
       </c>
       <c r="R8" t="n">
-        <v>4.6014</v>
+        <v>13.6314</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3254</v>
+        <v>-4.1634</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5985</v>
+        <v>-4.871</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7266</v>
+        <v>0.7075</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8389</v>
+        <v>0.5503</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5993</v>
+        <v>3.6116</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.4381</v>
+        <v>-3.0613</v>
       </c>
     </row>
     <row r="9">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.9577</v>
+        <v>-8.429500000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.645</v>
+        <v>-8.222999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6873</v>
+        <v>-0.2068000000000002</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6277</v>
+        <v>-1.0702</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4522</v>
+        <v>1.2796</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1754</v>
+        <v>-2.3499</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8323000000000003</v>
+        <v>2.1794</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1581000000000001</v>
+        <v>2.2914</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6742</v>
+        <v>-0.1120000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7953000000000001</v>
+        <v>-3.2496</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2941</v>
+        <v>-1.0115</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5012000000000001</v>
+        <v>-2.238</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0005</v>
+        <v>-3.3105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6013</v>
+        <v>-7.4001</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6008</v>
+        <v>4.0894</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3295</v>
+        <v>-3.4899</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2114</v>
+        <v>-3.002</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1182</v>
+        <v>-0.4876</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.839400000000001</v>
+        <v>-9.075099999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.807600000000001</v>
+        <v>-5.062</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0318</v>
+        <v>-4.0131</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.5353</v>
+        <v>-1.6492</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.096</v>
+        <v>3.5005</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.4394</v>
+        <v>-5.1499</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7155</v>
+        <v>9.2339</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6506</v>
+        <v>7.8291</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9351000000000003</v>
+        <v>1.405</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.8198</v>
+        <v>-10.8832</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4453</v>
+        <v>-4.3285</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.374499999999999</v>
+        <v>-6.5548</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4001999999999999</v>
+        <v>0.3894000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.4024</v>
+        <v>-13.8264</v>
       </c>
       <c r="R10" t="n">
-        <v>8.0023</v>
+        <v>14.2157</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.8638</v>
+        <v>-6.658799999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.349</v>
+        <v>-4.537100000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5147</v>
+        <v>-2.1218</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9598000000000002</v>
+        <v>-1.1564</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6593</v>
+        <v>4.0674</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6996</v>
+        <v>-5.2239</v>
       </c>
     </row>
     <row r="11">
@@ -1264,148 +1264,226 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.8991</v>
+        <v>-11.035</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.2338</v>
+        <v>-4.9761</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6653</v>
+        <v>-6.0588</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.751300000000001</v>
+        <v>-6.6251</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6162</v>
+        <v>-1.9234</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.1351</v>
+        <v>-4.701599999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9128</v>
+        <v>0.2150999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2581</v>
+        <v>1.6961</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.6548</v>
+        <v>-1.4809</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8385</v>
+        <v>-6.8402</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3582</v>
+        <v>-3.6195</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4804</v>
+        <v>-3.2208</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4001000000000001</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.6007</v>
+        <v>-4.6737</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2006</v>
+        <v>4.6736</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7492</v>
+        <v>-0.0467999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7203</v>
+        <v>-0.5177999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.02890000000000004</v>
+        <v>0.4708999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9985</v>
+        <v>-4.3632</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9985</v>
+        <v>-4.3632</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>D. HOGAN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OPOSITA MARÍN ENCE PEIXEGALEGO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-11.5313</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.6285</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-9.902799999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-4.230399999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7323000000000002</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4.9627</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.5836</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.2992</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-6.814</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.5669</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-5.2471</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3894000000000001</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-8.5684</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8.9579</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.7537999999999999</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-8.4444</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.8911</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-12.3353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>OPOSITA MARÍN ENCE PEIXEGALEGO</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4576999999999991</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-7.299200000000001</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7.7569</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-12.8828</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.7103</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-21.5929</v>
-      </c>
-      <c r="J12" t="n">
-        <v>23.1933</v>
-      </c>
-      <c r="K12" t="n">
-        <v>19.4412</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3.751700000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-36.0759</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-10.7311</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-25.3447</v>
-      </c>
-      <c r="P12" t="n">
-        <v>12.0035</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-46.01310000000001</v>
-      </c>
-      <c r="R12" t="n">
-        <v>58.0166</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.557200000000002</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1.8524</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.409299999999999</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-2.220299999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.3732</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-19.5933</v>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-13.2233</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.9709999999999941</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-12.2526</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-5.809399999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>18.1783</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-23.9878</v>
+      </c>
+      <c r="J13" t="n">
+        <v>63.4663</v>
+      </c>
+      <c r="K13" t="n">
+        <v>44.8203</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18.6463</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-69.27560000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-26.6415</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-42.6345</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14.605</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-79.84209999999999</v>
+      </c>
+      <c r="R13" t="n">
+        <v>94.4468</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-12.7363</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-17.1419</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.4063</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-9.283000000000001</v>
+      </c>
+      <c r="W13" t="n">
+        <v>32.5476</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-41.8305</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>18.0018</v>
+        <v>17.5457</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2486</v>
+        <v>15.3329</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7532</v>
+        <v>2.2127</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3509</v>
+        <v>5.556300000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0723999999999998</v>
+        <v>4.8047</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2784</v>
+        <v>0.7517000000000007</v>
       </c>
       <c r="J2" t="n">
-        <v>12.7341</v>
+        <v>17.5908</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8339</v>
+        <v>8.783099999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>8.9003</v>
+        <v>8.807599999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.3832</v>
+        <v>-12.0345</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.7614</v>
+        <v>-3.9785</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.6218</v>
+        <v>-8.056000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9737</v>
+        <v>6.621</v>
       </c>
       <c r="Q2" t="n">
-        <v>-8.957800000000001</v>
+        <v>-7.5948</v>
       </c>
       <c r="R2" t="n">
-        <v>9.9316</v>
+        <v>14.2158</v>
       </c>
       <c r="S2" t="n">
-        <v>6.176399999999999</v>
+        <v>-1.6398</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7408</v>
+        <v>-2.0626</v>
       </c>
       <c r="U2" t="n">
-        <v>4.4356</v>
+        <v>0.4228</v>
       </c>
       <c r="V2" t="n">
-        <v>6.500999999999999</v>
+        <v>7.0082</v>
       </c>
       <c r="W2" t="n">
-        <v>10.7316</v>
+        <v>7.3995</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.230700000000001</v>
+        <v>-0.3913000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>15.6554</v>
+        <v>12.4562</v>
       </c>
       <c r="E3" t="n">
-        <v>14.027</v>
+        <v>13.43</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6285</v>
+        <v>-0.9739000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>5.556300000000001</v>
+        <v>4.3509</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8047</v>
+        <v>0.0723999999999998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7517000000000007</v>
+        <v>4.2784</v>
       </c>
       <c r="J3" t="n">
-        <v>17.5908</v>
+        <v>12.7341</v>
       </c>
       <c r="K3" t="n">
-        <v>8.783099999999999</v>
+        <v>3.8339</v>
       </c>
       <c r="L3" t="n">
-        <v>8.807599999999999</v>
+        <v>8.9003</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.0345</v>
+        <v>-8.3832</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.9785</v>
+        <v>-3.7614</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.056000000000001</v>
+        <v>-4.6218</v>
       </c>
       <c r="P3" t="n">
-        <v>6.621</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.5948</v>
+        <v>-8.957800000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>14.2158</v>
+        <v>9.9316</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.5301</v>
+        <v>0.6308</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.3685</v>
+        <v>-1.078</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1614999999999999</v>
+        <v>1.7088</v>
       </c>
       <c r="V3" t="n">
-        <v>7.0082</v>
+        <v>6.500999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>7.3995</v>
+        <v>10.7316</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3913000000000001</v>
+        <v>-4.230700000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1253</v>
+        <v>4.1348</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5830999999999998</v>
+        <v>5.4232</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7084</v>
+        <v>-1.2885</v>
       </c>
       <c r="G4" t="n">
-        <v>1.925</v>
+        <v>2.2879</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1093</v>
+        <v>1.0483</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1843</v>
+        <v>1.2398</v>
       </c>
       <c r="J4" t="n">
-        <v>6.336499999999999</v>
+        <v>5.3927</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9907</v>
+        <v>3.364</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3458</v>
+        <v>2.0289</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.4114</v>
+        <v>-3.1048</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8815</v>
+        <v>-2.3156</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.53</v>
+        <v>-0.7891999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7527</v>
+        <v>7.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.4262</v>
+        <v>-0.1947</v>
       </c>
       <c r="R4" t="n">
-        <v>8.178900000000001</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0067</v>
+        <v>-0.7535999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0519</v>
+        <v>-0.9956</v>
       </c>
       <c r="U4" t="n">
-        <v>3.0586</v>
+        <v>0.2423</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5589999999999999</v>
+        <v>-4.994400000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1179</v>
+        <v>-6.2155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9405</v>
+        <v>3.4976</v>
       </c>
       <c r="E5" t="n">
-        <v>4.952500000000001</v>
+        <v>-0.5969</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.012</v>
+        <v>4.0944</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2879</v>
+        <v>1.925</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0483</v>
+        <v>3.1093</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2398</v>
+        <v>-1.1843</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3927</v>
+        <v>6.336499999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>3.364</v>
+        <v>4.9907</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0289</v>
+        <v>1.3458</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1048</v>
+        <v>-4.4114</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3156</v>
+        <v>-1.8815</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7891999999999999</v>
+        <v>-2.53</v>
       </c>
       <c r="P5" t="n">
-        <v>7.5947</v>
+        <v>1.7527</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1947</v>
+        <v>-6.4262</v>
       </c>
       <c r="R5" t="n">
-        <v>7.789400000000001</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9477</v>
+        <v>0.3789000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4663</v>
+        <v>-1.0659</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4812</v>
+        <v>1.4448</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.994400000000001</v>
+        <v>-0.5589999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2211</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.2155</v>
+        <v>-1.1179</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.7016</v>
+        <v>-3.4906</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5148</v>
+        <v>-1.4151</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1868</v>
+        <v>-2.0755</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8687</v>
@@ -922,13 +922,13 @@
         <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.306</v>
+        <v>-0.095</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2473</v>
+        <v>-0.1477</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.05860000000000001</v>
+        <v>0.05259999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-2.7216</v>
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.9228</v>
+        <v>-4.0716</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.0791</v>
+        <v>-7.7286</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1561</v>
+        <v>3.657</v>
       </c>
       <c r="G7" t="n">
         <v>0.4888000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>8.5684</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5305</v>
+        <v>-1.6793</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2860999999999999</v>
+        <v>-0.9358</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2443</v>
+        <v>-0.7434000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5445000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.251</v>
+        <v>-5.346799999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.132499999999999</v>
+        <v>-3.309199999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1185</v>
+        <v>-2.0374</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.9747</v>
+        <v>-1.6492</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4815</v>
+        <v>3.5005</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.456299999999999</v>
+        <v>-5.1499</v>
       </c>
       <c r="J8" t="n">
-        <v>5.4217</v>
+        <v>9.2339</v>
       </c>
       <c r="K8" t="n">
-        <v>6.918</v>
+        <v>7.8291</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4963</v>
+        <v>1.405</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.3962</v>
+        <v>-10.8832</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.4364</v>
+        <v>-4.3285</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.96</v>
+        <v>-6.5548</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3368</v>
+        <v>0.3894000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.2947</v>
+        <v>-13.8264</v>
       </c>
       <c r="R8" t="n">
-        <v>13.6314</v>
+        <v>14.2157</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.1634</v>
+        <v>-2.9304</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.871</v>
+        <v>-2.7844</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7075</v>
+        <v>-0.1461</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5503</v>
+        <v>-1.1564</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6116</v>
+        <v>4.0674</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0613</v>
+        <v>-5.2239</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.429500000000001</v>
+        <v>-5.901199999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.222999999999999</v>
+        <v>-6.1675</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2068000000000002</v>
+        <v>0.2662999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0702</v>
@@ -1156,13 +1156,13 @@
         <v>4.0894</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.4899</v>
+        <v>-0.9615</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.002</v>
+        <v>-0.9468999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4876</v>
+        <v>-0.01449999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5590000000000001</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.075099999999999</v>
+        <v>-6.196400000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.062</v>
+        <v>-5.4656</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0131</v>
+        <v>-0.7306000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6492</v>
+        <v>-5.9747</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5005</v>
+        <v>2.4815</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.1499</v>
+        <v>-8.456299999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>9.2339</v>
+        <v>5.4217</v>
       </c>
       <c r="K10" t="n">
-        <v>7.8291</v>
+        <v>6.918</v>
       </c>
       <c r="L10" t="n">
-        <v>1.405</v>
+        <v>-1.4963</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.8832</v>
+        <v>-11.3962</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.3285</v>
+        <v>-4.4364</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.5548</v>
+        <v>-6.96</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3894000000000001</v>
+        <v>2.3368</v>
       </c>
       <c r="Q10" t="n">
-        <v>-13.8264</v>
+        <v>-11.2947</v>
       </c>
       <c r="R10" t="n">
-        <v>14.2157</v>
+        <v>13.6314</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.658799999999999</v>
+        <v>-3.1089</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.537100000000001</v>
+        <v>-3.2043</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.1218</v>
+        <v>0.09530000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1564</v>
+        <v>0.5503</v>
       </c>
       <c r="W10" t="n">
-        <v>4.0674</v>
+        <v>3.6116</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.2239</v>
+        <v>-3.0613</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.035</v>
+        <v>-11.1477</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9761</v>
+        <v>-5.4506</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.0588</v>
+        <v>-5.697</v>
       </c>
       <c r="G11" t="n">
         <v>-6.6251</v>
@@ -1312,13 +1312,13 @@
         <v>4.6736</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0467999999999997</v>
+        <v>-0.1593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5177999999999999</v>
+        <v>-0.992</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4708999999999999</v>
+        <v>0.8326</v>
       </c>
       <c r="V11" t="n">
         <v>-4.3632</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.5313</v>
+        <v>-11.9206</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6285</v>
+        <v>-2.2404</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.902799999999999</v>
+        <v>-9.68</v>
       </c>
       <c r="G12" t="n">
         <v>-4.230399999999999</v>
@@ -1390,13 +1390,13 @@
         <v>8.9579</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7537999999999999</v>
+        <v>0.3645</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4653</v>
+        <v>-0.1467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2887</v>
+        <v>0.5113</v>
       </c>
       <c r="V12" t="n">
         <v>-8.4444</v>
@@ -1423,16 +1423,16 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.2233</v>
+        <v>-10.4406</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9709999999999941</v>
+        <v>1.812200000000006</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.2526</v>
+        <v>-12.2525</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.809399999999999</v>
+        <v>-5.809399999999998</v>
       </c>
       <c r="H13" t="n">
         <v>18.1783</v>
@@ -1450,7 +1450,7 @@
         <v>18.6463</v>
       </c>
       <c r="M13" t="n">
-        <v>-69.27560000000001</v>
+        <v>-69.2756</v>
       </c>
       <c r="N13" t="n">
         <v>-26.6415</v>
@@ -1468,13 +1468,13 @@
         <v>94.4468</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.7363</v>
+        <v>-9.9536</v>
       </c>
       <c r="T13" t="n">
-        <v>-17.1419</v>
+        <v>-14.3599</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4063</v>
+        <v>4.4065</v>
       </c>
       <c r="V13" t="n">
         <v>-9.283000000000001</v>
